--- a/exports/trend_1d/360ONE_full_report.xlsx
+++ b/exports/trend_1d/360ONE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:U39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>13.22</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42129</v>
+        <v>42130</v>
       </c>
       <c r="H2" t="n">
-        <v>53.5</v>
+        <v>52.1</v>
       </c>
       <c r="I2" t="n">
         <v>52.57687977066124</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.93</v>
+        <v>-3.52</v>
       </c>
       <c r="L2" t="n">
         <v>5.74</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>11.35</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42194</v>
+        <v>42195</v>
       </c>
       <c r="H3" t="n">
-        <v>53.95</v>
+        <v>55.2</v>
       </c>
       <c r="I3" t="n">
         <v>55.11380512052737</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.55</v>
+        <v>-5.95</v>
       </c>
       <c r="L3" t="n">
         <v>9.880000000000001</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>7.89</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H4" t="n">
-        <v>55.6</v>
+        <v>52.5</v>
       </c>
       <c r="I4" t="n">
         <v>53.78682471699308</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K4" t="n">
-        <v>0.72</v>
+        <v>-4.89</v>
       </c>
       <c r="L4" t="n">
-        <v>2.54</v>
+        <v>6.7</v>
       </c>
       <c r="M4" t="n">
-        <v>1.86</v>
+        <v>7.37</v>
       </c>
       <c r="N4" t="n">
-        <v>3.64</v>
+        <v>5.58</v>
       </c>
       <c r="O4" t="n">
         <v>2.32</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>12.27</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42303</v>
+        <v>42304</v>
       </c>
       <c r="H5" t="n">
-        <v>56.1</v>
+        <v>56.65</v>
       </c>
       <c r="I5" t="n">
         <v>56.22146310062902</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.86</v>
+        <v>-7.9</v>
       </c>
       <c r="L5" t="n">
-        <v>8.1</v>
+        <v>8.76</v>
       </c>
       <c r="M5" t="n">
         <v>1.39</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43748</v>
+        <v>43749</v>
       </c>
       <c r="H6" t="n">
-        <v>297.85</v>
+        <v>288.95</v>
       </c>
       <c r="I6" t="n">
         <v>293.1798577638356</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="K6" t="n">
-        <v>425.77</v>
+        <v>410.06</v>
       </c>
       <c r="L6" t="n">
         <v>3.8</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>49</v>
+      </c>
+      <c r="U6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>25.57</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43846</v>
+        <v>43847</v>
       </c>
       <c r="H7" t="n">
-        <v>302.2</v>
+        <v>339.2</v>
       </c>
       <c r="I7" t="n">
         <v>308.8648189513982</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.59</v>
+        <v>-17.39</v>
       </c>
       <c r="L7" t="n">
-        <v>17.06</v>
+        <v>19.48</v>
       </c>
       <c r="M7" t="n">
         <v>4.98</v>
       </c>
       <c r="N7" t="n">
-        <v>6.17</v>
+        <v>12.24</v>
       </c>
       <c r="O7" t="n">
         <v>-2.99</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>20.26</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43899</v>
+        <v>43901</v>
       </c>
       <c r="H8" t="n">
-        <v>350.3</v>
+        <v>349.65</v>
       </c>
       <c r="I8" t="n">
         <v>349.8666300061703</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K8" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="L8" t="n">
         <v>10.82</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>17.35</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43986</v>
+        <v>43987</v>
       </c>
       <c r="H9" t="n">
-        <v>239.85</v>
+        <v>250.15</v>
       </c>
       <c r="I9" t="n">
         <v>242.4609861850478</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K9" t="n">
-        <v>31.4</v>
+        <v>28.46</v>
       </c>
       <c r="L9" t="n">
         <v>1.82</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>17.01</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44111</v>
+        <v>44112</v>
       </c>
       <c r="H10" t="n">
-        <v>239.6</v>
+        <v>235.85</v>
       </c>
       <c r="I10" t="n">
         <v>236.4704027289986</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.22</v>
+        <v>-5.72</v>
       </c>
       <c r="L10" t="n">
         <v>9.27</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>13.02</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44149</v>
+        <v>44152</v>
       </c>
       <c r="H11" t="n">
-        <v>243.3</v>
+        <v>248.7</v>
       </c>
       <c r="I11" t="n">
         <v>244.4252041786311</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.16</v>
+        <v>-5.45</v>
       </c>
       <c r="L11" t="n">
-        <v>4.73</v>
+        <v>5.89</v>
       </c>
       <c r="M11" t="n">
         <v>2.07</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>11.28</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44299</v>
+        <v>44301</v>
       </c>
       <c r="H12" t="n">
-        <v>297.15</v>
+        <v>286.5</v>
       </c>
       <c r="I12" t="n">
         <v>288.1638731627705</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K12" t="n">
-        <v>19.48</v>
+        <v>15.2</v>
       </c>
       <c r="L12" t="n">
         <v>6.01</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>15.4</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44389</v>
+        <v>44390</v>
       </c>
       <c r="H13" t="n">
-        <v>305.95</v>
+        <v>308.9</v>
       </c>
       <c r="I13" t="n">
         <v>307.7916306209489</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K13" t="n">
-        <v>-6.79</v>
+        <v>-7.82</v>
       </c>
       <c r="L13" t="n">
         <v>13.35</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44522</v>
+        <v>44523</v>
       </c>
       <c r="H14" t="n">
-        <v>381.8</v>
+        <v>380.65</v>
       </c>
       <c r="I14" t="n">
         <v>381.1828172372735</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K14" t="n">
-        <v>23.6</v>
+        <v>23.23</v>
       </c>
       <c r="L14" t="n">
         <v>1.57</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>12.65</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44573</v>
+        <v>44574</v>
       </c>
       <c r="H15" t="n">
-        <v>393.55</v>
+        <v>396.55</v>
       </c>
       <c r="I15" t="n">
         <v>395.9077083366348</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.39</v>
+        <v>-4.18</v>
       </c>
       <c r="L15" t="n">
         <v>6.25</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>10.7</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H16" t="n">
-        <v>374.85</v>
+        <v>368.85</v>
       </c>
       <c r="I16" t="n">
         <v>372.6358094113758</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.47</v>
+        <v>-6.99</v>
       </c>
       <c r="L16" t="n">
-        <v>8.51</v>
+        <v>8.6</v>
       </c>
       <c r="M16" t="n">
         <v>3.61</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>14.96</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44651</v>
+        <v>44652</v>
       </c>
       <c r="H17" t="n">
-        <v>417.2</v>
+        <v>424.45</v>
       </c>
       <c r="I17" t="n">
         <v>417.3802413514572</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K17" t="n">
-        <v>-13.11</v>
+        <v>-15.07</v>
       </c>
       <c r="L17" t="n">
         <v>21.66</v>
       </c>
       <c r="M17" t="n">
-        <v>1.85</v>
+        <v>4.27</v>
       </c>
       <c r="N17" t="n">
         <v>3.52</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>11.4</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44691</v>
+        <v>44692</v>
       </c>
       <c r="H18" t="n">
-        <v>419.35</v>
+        <v>395.35</v>
       </c>
       <c r="I18" t="n">
         <v>399.9671587797004</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2</v>
+        <v>-6.86</v>
       </c>
       <c r="L18" t="n">
-        <v>4.23</v>
+        <v>8.32</v>
       </c>
       <c r="M18" t="n">
         <v>3.48</v>
       </c>
       <c r="N18" t="n">
-        <v>3.61</v>
+        <v>5.72</v>
       </c>
       <c r="O18" t="n">
         <v>1.74</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>21.69</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44742</v>
+        <v>44743</v>
       </c>
       <c r="H19" t="n">
-        <v>370.25</v>
+        <v>386.3</v>
       </c>
       <c r="I19" t="n">
         <v>384.8305132174601</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K19" t="n">
-        <v>6.35</v>
+        <v>2.29</v>
       </c>
       <c r="L19" t="n">
         <v>10.03</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>15.67</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44978</v>
+        <v>44979</v>
       </c>
       <c r="H20" t="n">
-        <v>453.2</v>
+        <v>446.3</v>
       </c>
       <c r="I20" t="n">
         <v>448.0134749259815</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K20" t="n">
-        <v>17.32</v>
+        <v>15.53</v>
       </c>
       <c r="L20" t="n">
         <v>5.59</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>161</v>
+        <v>162</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.85</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45091</v>
+        <v>45092</v>
       </c>
       <c r="H21" t="n">
-        <v>438.5</v>
+        <v>439.45</v>
       </c>
       <c r="I21" t="n">
         <v>438.7638316196357</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K21" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="L21" t="n">
         <v>9.779999999999999</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.05</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45202</v>
+        <v>45203</v>
       </c>
       <c r="H22" t="n">
-        <v>501.4</v>
+        <v>496.75</v>
       </c>
       <c r="I22" t="n">
         <v>497.3003896989828</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K22" t="n">
-        <v>14.1</v>
+        <v>13.04</v>
       </c>
       <c r="L22" t="n">
         <v>4.46</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>9.85</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45212</v>
+        <v>45215</v>
       </c>
       <c r="H23" t="n">
-        <v>537.85</v>
+        <v>553.1</v>
       </c>
       <c r="I23" t="n">
         <v>541.5691465233992</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.27</v>
+        <v>-11.34</v>
       </c>
       <c r="L23" t="n">
-        <v>8.710000000000001</v>
+        <v>11.77</v>
       </c>
       <c r="M23" t="n">
         <v>1.19</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>10.43</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H24" t="n">
-        <v>637.65</v>
+        <v>619</v>
       </c>
       <c r="I24" t="n">
         <v>626.8677965930251</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K24" t="n">
-        <v>15.29</v>
+        <v>11.91</v>
       </c>
       <c r="L24" t="n">
         <v>9.25</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>12.43</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45334</v>
+        <v>45335</v>
       </c>
       <c r="H25" t="n">
-        <v>648.25</v>
+        <v>691.7</v>
       </c>
       <c r="I25" t="n">
         <v>676.5765669048276</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.73</v>
+        <v>-11.74</v>
       </c>
       <c r="L25" t="n">
-        <v>8.19</v>
+        <v>12.76</v>
       </c>
       <c r="M25" t="n">
         <v>1.81</v>
       </c>
       <c r="N25" t="n">
-        <v>2.32</v>
+        <v>6.7</v>
       </c>
       <c r="O25" t="n">
         <v>-2.92</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.82</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45372</v>
+        <v>45373</v>
       </c>
       <c r="H26" t="n">
-        <v>673.4</v>
+        <v>665.85</v>
       </c>
       <c r="I26" t="n">
         <v>668.2966381246899</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.65</v>
+        <v>-3.74</v>
       </c>
       <c r="L26" t="n">
         <v>6.46</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>12.86</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45391</v>
+        <v>45392</v>
       </c>
       <c r="H27" t="n">
-        <v>719.15</v>
+        <v>735.8</v>
       </c>
       <c r="I27" t="n">
         <v>734.8589405662658</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K27" t="n">
-        <v>-8</v>
+        <v>-10.51</v>
       </c>
       <c r="L27" t="n">
         <v>12.4</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.79</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H28" t="n">
-        <v>1014.05</v>
+        <v>955.45</v>
       </c>
       <c r="I28" t="n">
         <v>994.2606970287258</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K28" t="n">
-        <v>37.82</v>
+        <v>29.85</v>
       </c>
       <c r="L28" t="n">
         <v>6.03</v>
@@ -2037,7 +2372,7 @@
         <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>5.17</v>
+        <v>5.78</v>
       </c>
       <c r="O28" t="n">
         <v>2.32</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>119</v>
+        <v>120</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>7</v>
+      </c>
+      <c r="U28" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>16.5</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45579</v>
+        <v>45580</v>
       </c>
       <c r="H29" t="n">
-        <v>1063.6</v>
+        <v>1114.75</v>
       </c>
       <c r="I29" t="n">
         <v>1113.059335567321</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K29" t="n">
-        <v>-11.32</v>
+        <v>-16.67</v>
       </c>
       <c r="L29" t="n">
-        <v>14.96</v>
+        <v>17.21</v>
       </c>
       <c r="M29" t="n">
         <v>4.16</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>15.75</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="H30" t="n">
-        <v>1166.55</v>
+        <v>1129.1</v>
       </c>
       <c r="I30" t="n">
         <v>1159.598002014919</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K30" t="n">
-        <v>4.65</v>
+        <v>1.29</v>
       </c>
       <c r="L30" t="n">
         <v>11.91</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>15.44</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45768</v>
+        <v>45769</v>
       </c>
       <c r="H31" t="n">
-        <v>954.25</v>
+        <v>1013.9</v>
       </c>
       <c r="I31" t="n">
         <v>986.2522775605235</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K31" t="n">
-        <v>15.49</v>
+        <v>10.2</v>
       </c>
       <c r="L31" t="n">
         <v>9.289999999999999</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>18.91</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="H32" t="n">
-        <v>1118.6</v>
+        <v>1077.9</v>
       </c>
       <c r="I32" t="n">
         <v>1108.636139410263</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K32" t="n">
-        <v>10.33</v>
+        <v>6.31</v>
       </c>
       <c r="L32" t="n">
         <v>12.95</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>13.07</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="H33" t="n">
-        <v>1084.4</v>
+        <v>1095.1</v>
       </c>
       <c r="I33" t="n">
         <v>1090.455914009884</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.6</v>
+        <v>-1.6</v>
       </c>
       <c r="L33" t="n">
         <v>3.88</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>7.64</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="H34" t="n">
-        <v>1119.6</v>
+        <v>1080.7</v>
       </c>
       <c r="I34" t="n">
         <v>1091.448795171815</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>2.24</v>
+        <v>-1.31</v>
       </c>
       <c r="L34" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="M34" t="n">
         <v>2.15</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>10.78</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45987</v>
+        <v>45988</v>
       </c>
       <c r="H35" t="n">
-        <v>1150</v>
+        <v>1166.6</v>
       </c>
       <c r="I35" t="n">
         <v>1151.704827257084</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.41</v>
+        <v>-7.95</v>
       </c>
       <c r="L35" t="n">
-        <v>7.19</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M35" t="n">
         <v>1.01</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="H36" t="n">
-        <v>1129.6</v>
+        <v>1095.3</v>
       </c>
       <c r="I36" t="n">
         <v>1105.098108811019</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.17</v>
+        <v>-6.11</v>
       </c>
       <c r="L36" t="n">
-        <v>6.34</v>
+        <v>6.73</v>
       </c>
       <c r="M36" t="n">
         <v>0.6899999999999999</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>13.35</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H37" t="n">
-        <v>1009.5</v>
+        <v>1056</v>
       </c>
       <c r="I37" t="n">
         <v>1019.332746998673</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K37" t="n">
-        <v>7.83</v>
+        <v>3.59</v>
       </c>
       <c r="L37" t="n">
         <v>8.51</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>12.16</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="H38" t="n">
-        <v>1136.9</v>
+        <v>1110</v>
       </c>
       <c r="I38" t="n">
         <v>1121.090162393051</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K38" t="n">
-        <v>7.66</v>
+        <v>5.11</v>
       </c>
       <c r="L38" t="n">
         <v>4.45</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -2667,6 +3134,14 @@
       <c r="Q39" t="n">
         <v>34</v>
       </c>
+      <c r="R39" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6163,7 +6638,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>113.6</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6">
@@ -6173,7 +6648,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
@@ -6183,7 +6658,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="8">
@@ -6193,7 +6668,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -6203,7 +6678,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
@@ -6213,7 +6688,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>145.8</v>
+        <v>147.2</v>
       </c>
     </row>
     <row r="11">
@@ -6253,7 +6728,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.77</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="15">
@@ -6263,7 +6738,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29.72</v>
+        <v>26.08</v>
       </c>
     </row>
     <row r="16">
@@ -6273,7 +6748,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6758,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>425.77</v>
+        <v>410.06</v>
       </c>
     </row>
     <row r="18">
@@ -6293,7 +6768,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.6</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="19">
@@ -6303,7 +6778,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.039999999999999</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -6313,7 +6788,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="21">
@@ -6333,7 +6808,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -6343,7 +6818,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -6353,7 +6828,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.23</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="25">
@@ -6373,7 +6848,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.07</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="27">
@@ -6383,7 +6858,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.92</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="28">
@@ -6393,7 +6868,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
